--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44126</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44791</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45208</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44992</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>44872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45322</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44489</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44096</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45387</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>45736</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44729</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44984</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45341</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44209</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44160</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44334</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44245</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44152</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44875</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44732</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44813</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>44063</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44186</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44218</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44201</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44272</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44174</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44326</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>44186</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44452</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44298</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44755</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>44713</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44424</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>44445</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44194</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44412</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44168</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44199</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44332</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44351</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44813</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44426</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44575</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44819</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44179</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44376</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44102</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44065.75936342592</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44690</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44644</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44111</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44083</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44068</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44183</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44071</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44627</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44180</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44467</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44102</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44238</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44167</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44789</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44508</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44546</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44082</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44053</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44424</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44078</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44265</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44272</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44259</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44722</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44756</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44173</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44511</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44407</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44460</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44839</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44879</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44298</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44447</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44532</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44648</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44376</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44182</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44608</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44417</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44481</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44875</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44474</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44179</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44494</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44343</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44187</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44420</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>44068</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44371</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44441</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44868</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44417</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44064</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44414</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44428</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44685</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44116</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44820</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44468</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44698</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44139</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44620</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44420</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44068</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44312</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44096</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>44578</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44445</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44089</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44756</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>44596</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45622</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44239</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45680</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>44055</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45139</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45117</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45117</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44250</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45341</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45329</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45002</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45362</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44070</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45173</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44313</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44820</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44490</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44426</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44102</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44875</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44984</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45688</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44124</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44790</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45771</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45097</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45091</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>44134</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44147</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45432</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45261</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>44211</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44971</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45439</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45601</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>44168</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>44435</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44062</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45229</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44258</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45755</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45075</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45110</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44181</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45117</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45261</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45103</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44935</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45034</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44053</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45574</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45002</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45467</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45467</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45467</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>44988</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45103</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45085</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45443</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44634</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45711</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44082</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44467</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45559</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45691</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45559</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45170</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44895</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44901.44221064815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44967</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45457</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45755</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44448</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>44953</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>44904</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45005</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45772</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44949</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45002</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44936</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45670</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45519</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45777</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44091</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44911</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45329</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44895</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45275</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44945</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>44524</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44095</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45049</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45097</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45362</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44134</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45594</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45252</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45590</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>44995</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44783</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45671</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45511</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45561</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44928</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45001</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45418</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44783</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45230</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45266</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45014</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44676</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44575</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45345</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44620</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45264</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45160</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>44939</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45155</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45631</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>45345</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45752.63438657407</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44936</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45568</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45155</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45155</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>45439</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45559</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45559</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44169</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45152</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45691.70575231482</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45071</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44582</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45191</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45344</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45078</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44470</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45182</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44683</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>44963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>44229</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45091</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45677.59434027778</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45798</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44685</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44685</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45082</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45182</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44454</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44624</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>45547</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45833</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44463</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44462</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45579</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45574</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45574</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>45574.59</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44984</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45215</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45637.70998842592</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45007</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45608</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>44152</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45138</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>44820</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45727</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45211</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45061</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45183</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45183</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45117</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>44302</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44728</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>44728</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45547</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>44705</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>44951</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44265</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45677.58091435185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45164</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>45701.45637731482</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>45117</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45299</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45303</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>44055</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45756</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45726.39961805556</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45775</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44804</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45299</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45266</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>45722</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45306</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>44994</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44078</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>44495</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>44804</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45705.39993055556</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>44756</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45399</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>44070</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>44867</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>44950</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>45036</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45082</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45825.71435185185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>44529</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>44068</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45825.44564814815</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>44078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>44391</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45688</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45264</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>44937</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45726.40262731481</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>45772</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45201</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>44609</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45873</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45303</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45399</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52852,7 +52852,7 @@
         <v>45616</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45429</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53142,7 +53142,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53199,7 +53199,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45574</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44984</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>44602</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>44425</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44110</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>44145</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>44316</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>44370</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>44967</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>44967</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>44090</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>44075</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54748,7 +54748,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45568</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>44137</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45188</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>44110</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         <v>45002</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44071</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>44938</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>44698</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55774,7 +55774,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56002,7 +56002,7 @@
         <v>45036</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56059,7 +56059,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>45447</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56344,7 +56344,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>44900</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>45474</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>44904</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>45261</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>44159</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45547</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>45005</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>44965</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>44964</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>44343</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57836,7 +57836,7 @@
         <v>45051</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>44102</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44126</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44791</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45208</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44992</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>44872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45322</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>44489</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44096</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45387</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>45736</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44729</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45182</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44984</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45341</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44209</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44160</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44334</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44245</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44152</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44875</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44732</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44813</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>44063</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44186</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44218</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44201</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44272</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44174</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44326</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>44186</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44452</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44298</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44755</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>44713</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44424</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>44445</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44194</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44412</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44168</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44199</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44332</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44351</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44813</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44426</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44575</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44285</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44819</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44179</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44376</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44102</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44065.75936342592</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44690</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44644</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44111</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44083</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44068</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44183</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44071</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44627</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44180</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44467</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44102</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44238</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44167</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44789</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44508</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44546</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44082</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44053</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44424</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44078</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44265</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44272</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44259</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44722</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44756</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44173</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44511</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44407</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44460</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44839</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44879</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44298</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44447</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44532</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44455</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44489</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44648</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44376</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44182</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44608</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44417</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44481</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44875</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44106</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44474</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>44179</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44494</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44343</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44187</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44791</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44420</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>44068</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44371</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44441</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44868</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44417</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44064</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44414</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44428</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44685</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44116</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44820</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44468</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44698</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44139</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44620</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44420</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44068</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44312</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44096</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>44578</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44445</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44089</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44756</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>44596</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45622</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44239</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45680</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>44055</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45139</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45117</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16538,7 +16538,7 @@
         <v>45117</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44250</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45341</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45329</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45002</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45362</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44070</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>45173</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44313</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44820</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44490</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45071</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44426</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44102</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44875</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44984</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45688</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44124</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44790</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45771</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45097</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45091</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19460,7 +19460,7 @@
         <v>45082</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>44134</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44147</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45432</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45261</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>44211</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44971</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45439</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45601</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>44168</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>44435</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>44062</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45229</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>44258</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45755</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45075</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45110</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44181</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45117</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45117</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45261</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45103</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44935</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45034</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44053</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45574</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45002</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45467</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45467</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45467</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45328</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>44988</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45103</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45085</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45443</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44634</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45711</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44082</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44467</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45559</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45691</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45559</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45170</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44895</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44901.44221064815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44967</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45457</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45755</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44448</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>44953</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>44904</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45005</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45772</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>44949</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45002</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44936</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45670</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45519</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45777</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44091</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44911</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45329</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44895</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45275</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44945</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>44524</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44095</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45049</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45097</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45362</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44134</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>44111</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45594</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45252</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45590</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45546</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>44995</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45679</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44783</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32162,7 +32162,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>45671</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45511</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>45561</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>44928</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45001</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45418</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44783</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45230</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>45266</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45012</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45014</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>44676</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44575</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>45345</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44620</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45264</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45160</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>44939</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45155</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45631</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>45345</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45752.63438657407</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44936</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45568</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>44795</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45155</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45155</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>45439</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>45559</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45559</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44169</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45152</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45691.70575231482</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45071</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44582</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45191</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45344</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45078</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44470</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45182</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44683</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>44963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>44229</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45091</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45677.59434027778</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45798</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44685</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44685</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45082</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45182</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>44454</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44624</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>45547</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45833</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>44463</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>44462</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45579</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45574</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45574</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>45574.59</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>44984</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45215</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45637.70998842592</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45007</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45608</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>44152</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45138</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>44820</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45727</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45211</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45061</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45183</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45183</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45117</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>44302</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44728</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>44728</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45164,7 +45164,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45392,7 +45392,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>45093</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45547</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>44705</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>44951</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>44852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45962,7 +45962,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>44265</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45677.58091435185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45164</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>45701.45637731482</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>45117</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45236</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45299</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>45303</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47563,7 +47563,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>44055</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45756</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45726.39961805556</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48024,7 +48024,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48148,7 +48148,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45775</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>44804</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45299</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45266</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>45722</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45306</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>44994</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>44078</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>44495</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>44804</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45705.39993055556</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49350,7 +49350,7 @@
         <v>44756</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49521,7 +49521,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45399</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>44070</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>44867</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>44950</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>45036</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45082</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45825.71435185185</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>44529</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>44068</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45825.44564814815</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>44078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45188</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>44391</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45688</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45264</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>44937</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45726.40262731481</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>45772</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>45201</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>44609</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45873</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45303</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45399</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52852,7 +52852,7 @@
         <v>45616</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45429</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53142,7 +53142,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53199,7 +53199,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45574</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53370,7 +53370,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53427,7 +53427,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53598,7 +53598,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53712,7 +53712,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>44984</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53826,7 +53826,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53883,7 +53883,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>44602</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>44425</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44110</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>44145</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>44316</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>44370</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>44967</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>44967</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>44090</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>44075</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54748,7 +54748,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54805,7 +54805,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>45568</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>44137</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45188</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>44110</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         <v>45002</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44071</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55375,7 +55375,7 @@
         <v>44938</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>44698</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55603,7 +55603,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55660,7 +55660,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55774,7 +55774,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56002,7 +56002,7 @@
         <v>45036</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56059,7 +56059,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>45447</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56344,7 +56344,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>44900</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>45474</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>44904</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56691,7 +56691,7 @@
         <v>45261</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56924,7 +56924,7 @@
         <v>44159</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45547</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57209,7 +57209,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>45005</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>44965</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>44964</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57665,7 +57665,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57779,7 +57779,7 @@
         <v>44343</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57836,7 +57836,7 @@
         <v>45051</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>44102</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44126</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44791</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45208</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44992</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44872</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44489</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>45736</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45182</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44096</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44729</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44984</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>45341</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45322</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44209</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44160</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44334</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44245</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44152</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44732</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44875</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44813</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>44063</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44186</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44218</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44201</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44272</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44326</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44186</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44452</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44298</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44755</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44713</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44424</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>44445</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44194</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44412</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44332</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44168</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44199</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44351</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44813</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44426</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44575</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44819</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44285</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44179</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44376</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44065.75936342592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44102</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44690</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44111</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44644</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44627</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44083</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44183</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44071</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44068</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44180</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44102</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44467</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44238</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44167</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44789</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44508</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44173</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44546</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44082</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44424</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44265</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44078</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44272</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44259</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44756</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44722</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44511</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44407</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44460</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44839</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44879</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44298</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44447</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44532</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44648</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44376</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44182</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44608</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44417</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44481</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44106</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44494</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44179</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44343</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44187</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44791</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44420</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44068</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44441</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>44417</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44064</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44868</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44414</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44685</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44428</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44116</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44820</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44468</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44698</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44139</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44523</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44068</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44620</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44420</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44312</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44096</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44089</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44089</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>44756</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44578</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44875</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44596</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44239</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44102</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44875</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45170</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44250</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>44895</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44901.44221064815</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45341</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45329</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44967</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45097</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45091</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45362</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45432</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44448</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45173</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44313</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44953</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>44820</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44490</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44904</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44062</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45519</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45772</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45777</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>44949</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45002</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45275</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>44945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44524</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44095</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45049</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45097</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45594</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45252</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45590</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45546</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45679</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>44783</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45511</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44783</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45230</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45266</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45345</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44407</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45345</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44575</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44620</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45160</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45155</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45631</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45752.63438657407</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44795</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45798</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45559</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45559</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45152</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44582</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45191</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45078</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>44181</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45117</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45117</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>44683</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45677.59434027778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45175</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45727</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45082</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45467</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45467</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45467</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45085</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>44624</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45547</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44082</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44467</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45215</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>44152</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45138</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>44820</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45211</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45005</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45183</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45183</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45117</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44302</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44728</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44728</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44936</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44091</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>44911</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45329</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44895</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45362</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44705</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44852</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44134</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44265</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45164</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45117</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45236</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45299</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>45303</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44995</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45825.71435185185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45671</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45756</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45561</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45825.44564814815</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44928</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45001</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45418</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45726.39961805556</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45775</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>45299</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>45266</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45306</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45012</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45014</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>44676</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>44609</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45264</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>44939</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45873</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44756</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45399</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44867</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44950</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>45082</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>44936</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45264</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45568</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45201</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45833</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45303</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45399</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45616</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45155</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45155</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45880</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45429</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45439</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45877</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45574</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>44169</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45841</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45691.70575231482</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45071</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>44984</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45344</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>44470</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>45182</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>44602</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>44963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>44229</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>44425</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45091</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>44110</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>44685</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>44685</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>44145</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45182</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>44316</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42569,7 +42569,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>44370</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>44454</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>44967</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44090</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>44463</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45568</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>44137</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>44462</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45579</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45188</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45574</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45574</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45574.59</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>44984</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45637.70998842592</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>44110</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45007</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45002</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45608</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>44071</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44698</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45447</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45093</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45547</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>44900</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45474</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>44904</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45261</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>44951</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44159</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45547</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45677.58091435185</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45005</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45701.45637731482</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>44965</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44964</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45722</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>44343</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45051</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44994</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44078</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>44495</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45705.39993055556</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>44070</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44102</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>45036</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>44529</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45680</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>44068</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45139</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>45117</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45117</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>44078</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>44391</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45688</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>44937</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45726.40262731481</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45772</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45622</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>44426</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>44984</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45688</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53107,7 +53107,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>44124</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45002</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45771</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>44070</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>45071</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45071</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>44971</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>45601</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>44790</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54713,7 +54713,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>44258</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54951,7 +54951,7 @@
         <v>45082</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45755</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>44134</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>44147</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55350,7 +55350,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45261</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>44211</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45439</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>44168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55811,7 +55811,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>44435</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>44935</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>45034</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45574</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45002</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45229</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>44988</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45443</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>45075</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45110</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56842,7 +56842,7 @@
         <v>44634</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45711</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>45691</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45103</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57422,7 +57422,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57479,7 +57479,7 @@
         <v>45559</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57774,7 +57774,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45103</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45457</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45755</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45559</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44126</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>44791</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>45208</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44992</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>44872</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44489</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>45736</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45182</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>44096</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44729</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44984</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>45341</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45322</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44209</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44160</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44334</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44245</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44152</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44732</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>44875</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44813</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>44063</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44186</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>44218</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44201</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>44272</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>44326</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>44186</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>44452</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44298</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44755</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44713</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>44424</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>44445</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44194</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44412</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>44332</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44168</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>44199</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44351</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44813</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>44426</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44575</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44819</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>44285</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44179</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44376</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44065.75936342592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44102</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44690</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44111</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44644</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44627</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44083</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44183</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44071</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44068</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44180</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44102</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44467</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44238</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44167</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44789</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44508</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44173</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44546</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44082</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44424</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44265</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44078</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44272</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44259</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44756</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44722</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44511</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44407</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44460</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44839</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44879</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44298</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44447</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44532</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44455</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44489</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44648</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44376</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44798</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44182</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44608</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44417</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>44481</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44106</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44494</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>44179</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44343</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44187</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44791</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44420</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44068</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44371</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44441</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>44417</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44064</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44868</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44414</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44685</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44428</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44116</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44820</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44468</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>44698</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>44139</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44523</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44068</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44620</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>44420</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44312</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44096</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44089</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44445</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44089</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>44756</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44578</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44875</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>44596</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>44239</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44102</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>44875</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45170</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44250</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>44895</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44901.44221064815</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45341</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45329</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>44967</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45097</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45091</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45362</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45432</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44448</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45173</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44313</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>44953</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>44820</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>44490</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44904</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44062</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45670</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45519</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45772</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45777</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>44949</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45002</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45275</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>44945</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44524</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44095</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45049</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45097</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45594</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45252</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45590</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45546</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45679</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>44783</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45511</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22065,7 +22065,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44783</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45230</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45266</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45345</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44407</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45345</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44575</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44620</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45160</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45155</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45631</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45752.63438657407</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>44795</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45798</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45559</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45559</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>45152</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44582</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45191</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45078</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>44181</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45117</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45117</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>44683</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45677.59434027778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45175</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45727</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45082</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45467</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45467</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45467</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>45085</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>44624</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45547</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44082</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>44467</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45215</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>44152</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45138</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>44820</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>45211</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>45005</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45183</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45183</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45117</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>44302</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30965,7 +30965,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44728</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>44728</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>44936</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44091</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>44911</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>45329</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>44895</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>45362</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>44705</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44852</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>44134</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44265</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45164</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33022,7 +33022,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45117</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45236</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45299</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33654,7 +33654,7 @@
         <v>45303</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>44995</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45825.71435185185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34167,7 +34167,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45671</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45756</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>45561</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45825.44564814815</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44928</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45001</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45418</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45726.39961805556</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>45775</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35104,7 +35104,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>44804</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>45299</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>45266</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45306</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45012</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45014</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>44676</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36021,7 +36021,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>44609</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36140,7 +36140,7 @@
         <v>45264</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>44939</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>44804</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45873</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44756</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45399</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>44867</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>44950</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37684,7 +37684,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>45082</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37917,7 +37917,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>44936</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45264</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45568</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>45201</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         <v>45833</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>45303</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45399</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45616</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39186,7 +39186,7 @@
         <v>45155</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45155</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45880</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45429</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45439</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45877</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45574</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>44169</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45841</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45691.70575231482</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45071</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>44984</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45344</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>44470</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>45182</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>44602</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>44963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>44229</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>44425</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         <v>45091</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>44110</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>44685</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>44685</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42113,7 +42113,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>44145</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45182</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>44316</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42569,7 +42569,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>44370</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>44454</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42797,7 +42797,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>44967</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
         <v>44090</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>44075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>44463</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45568</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>44137</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>44462</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>45579</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43999,7 +43999,7 @@
         <v>45188</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45574</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45574</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45574.59</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>44984</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45637.70998842592</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>44110</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45007</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45002</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45608</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>44071</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44938</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44698</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45061</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45447</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45093</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45547</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>44900</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45474</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>44904</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45261</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>44951</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44159</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45547</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45677.58091435185</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45005</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45701.45637731482</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>44965</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44964</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49164,7 +49164,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49221,7 +49221,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45722</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>44343</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45051</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44994</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44078</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>44495</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45705.39993055556</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>44070</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44102</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>45036</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>44529</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45680</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>44068</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45139</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>45117</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45117</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>44078</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>45188</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51449,7 +51449,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>44391</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51620,7 +51620,7 @@
         <v>45688</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>44937</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45726.40262731481</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51853,7 +51853,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51910,7 +51910,7 @@
         <v>45772</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45622</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>44426</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52822,7 +52822,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>44984</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53050,7 +53050,7 @@
         <v>45688</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53107,7 +53107,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>44124</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53221,7 +53221,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45002</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53335,7 +53335,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45771</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>44070</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>45071</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45071</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53910,7 +53910,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54024,7 +54024,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>44971</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54138,7 +54138,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>45601</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54366,7 +54366,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54542,7 +54542,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54599,7 +54599,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>44790</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54713,7 +54713,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54770,7 +54770,7 @@
         <v>44258</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54951,7 +54951,7 @@
         <v>45082</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55008,7 +55008,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>45755</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>44134</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>44147</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55350,7 +55350,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45261</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55521,7 +55521,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>44211</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45439</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>44168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55811,7 +55811,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>44435</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55925,7 +55925,7 @@
         <v>44935</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>45034</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56096,7 +56096,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56153,7 +56153,7 @@
         <v>45574</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45002</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56324,7 +56324,7 @@
         <v>45328</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>45229</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>44988</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45443</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56723,7 +56723,7 @@
         <v>45075</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45110</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56842,7 +56842,7 @@
         <v>44634</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45711</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>45261</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>45691</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57365,7 +57365,7 @@
         <v>45103</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57422,7 +57422,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57479,7 +57479,7 @@
         <v>45559</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57774,7 +57774,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45103</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45457</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>45755</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45559</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -58354,7 +58354,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44126</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44791</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>44992</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44984</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44489</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>45182</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45736</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44729</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>44096</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45341</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45322</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44209</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44160</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>44334</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44245</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44152</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44732</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44875</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44813</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>44186</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44218</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44272</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>44326</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44174</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44186</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44452</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44755</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44713</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44424</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44298</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44194</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44412</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44168</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44199</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44351</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44813</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44426</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44575</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44819</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44285</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44179</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44376</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44102</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44690</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44865</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44644</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44627</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44438</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44083</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44068</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44183</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44071</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44467</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44102</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44238</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44238</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44292</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44180</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44167</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44789</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44508</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44173</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44546</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44082</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44424</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44078</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44265</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44272</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44756</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>44722</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44511</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44407</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44460</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44839</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44879</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44298</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44447</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>44532</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44455</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>44489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44376</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44648</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44798</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44182</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44417</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44481</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44875</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44106</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44179</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44343</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44474</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44187</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44494</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44791</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44420</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>44068</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>44868</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>44414</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44441</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44428</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>44417</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44371</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44685</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44468</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>44698</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>44820</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44139</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44523</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44068</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44420</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44620</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44312</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44096</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44578</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44756</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44596</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44445</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44239</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45547</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45264</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44448</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45688</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45303</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44728</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44089</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45711</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45075</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45561</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44089</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44068</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44152</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44575</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>44090</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45071</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44967</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>44676</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45082</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45701.45637731482</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>44102</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45097</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44895</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44181</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44965</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>44967</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44950</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45457</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45399</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45399</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>44169</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45439</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45688</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45182</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45771</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44756</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44953</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44435</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45002</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45034</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45091</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>44971</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44137</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45117</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45117</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45568</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45061</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45117</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45117</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45188</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>44316</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>44425</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45303</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45601</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44110</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44967</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44904</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44620</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45755</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45306</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45002</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45002</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45344</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45616</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45275</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45175</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44470</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44995</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45622</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45117</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45547</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45005</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45608</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45519</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45670</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>44529</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45777</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45447</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45155</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45155</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>44147</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45261</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>44495</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45546</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45429</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45164</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45705.39993055556</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44490</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44467</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45261</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44783</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45266</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44928</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45071</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45103</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45679</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45230</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44783</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45511</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>44804</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>44804</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45345</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45252</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44407</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45594</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45345</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45590</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45167</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44683</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45772</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44463</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>44102</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44229</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45362</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>44939</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>44078</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45014</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44134</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>44936</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45160</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>44900</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45139</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>44820</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45078</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44937</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>44426</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45328</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44582</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>44728</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45007</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45574.59</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45173</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45798</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45727</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45341</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45191</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45085</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>44820</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44095</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44111</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>44963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45097</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>44984</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>44159</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45418</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45756</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45439</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45036</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>44624</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45299</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>44875</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45001</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44370</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>45049</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>44124</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>44911</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44313</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44945</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>44949</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45155</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45579</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45568</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45772</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45036</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>44302</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>44145</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>44082</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45329</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44524</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45103</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>44265</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45722</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45183</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>44391</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45873</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45474</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45726.39961805556</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>44609</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>44168</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45559</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45201</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>44110</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44250</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>44454</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>44936</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45152</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45680</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>44852</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45574</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45467</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49373,7 +49373,7 @@
         <v>45467</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>45467</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>45215</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45547</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>44795</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45443</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45880</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50176,7 +50176,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>44984</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45082</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45833</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45877</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>44070</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>44075</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45841</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45559</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>44867</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45188</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>44634</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>44071</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>44078</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45559</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>44462</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>44070</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45329</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45432</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52999,7 +52999,7 @@
         <v>45887.57631944444</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53056,7 +53056,7 @@
         <v>45887.58039351852</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>45091</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53170,7 +53170,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53341,7 +53341,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>45266</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>44698</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>44904</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45887.54020833333</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>44964</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>45012</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54325,7 +54325,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>44602</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54439,7 +54439,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>45051</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>45211</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>44258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55123,7 +55123,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45890.36122685186</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         <v>44685</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>44685</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>45671</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>44790</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
         <v>45755</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>44091</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55869,7 +55869,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>44343</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55983,7 +55983,7 @@
         <v>45264</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56154,7 +56154,7 @@
         <v>45093</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45138</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>44984</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45559</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>44895</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56553,7 +56553,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56724,7 +56724,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>44211</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56895,7 +56895,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56952,7 +56952,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>45005</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45574</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45574</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45574</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>44935</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45631</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>44134</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45117</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>45002</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57693,7 +57693,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>45229</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44126</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>45208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44791</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>44992</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44872</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>44984</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44489</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>45182</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45736</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>44729</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>44096</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45341</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45322</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44209</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44160</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>44334</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>44245</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>44152</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44732</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44875</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44813</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>44186</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>44218</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>44201</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44272</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>44326</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44174</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>44186</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44452</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>44755</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44713</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>44424</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44298</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44194</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>44332</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44412</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44168</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>44199</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44351</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44813</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44426</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44575</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44819</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44285</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44179</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44376</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44102</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44690</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44865</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44111</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44644</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44627</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>44438</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44083</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>44068</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44183</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44071</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44467</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44102</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44238</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44238</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>44292</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44180</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>44167</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44789</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44508</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44173</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44546</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44082</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44424</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44078</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44265</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44272</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         <v>44756</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>44722</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44511</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44407</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44460</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44839</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>44879</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44298</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44447</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>44532</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>44455</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>44489</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44376</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44648</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44798</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44182</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         <v>44608</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44417</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44481</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44875</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44106</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>44179</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44343</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44474</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44187</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44494</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44791</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44420</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>44068</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>44868</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>44414</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44441</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>44428</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>44417</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>44371</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>44685</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>44468</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>44698</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>44820</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44139</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>44523</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44068</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44420</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>44620</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44312</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44096</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44578</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44756</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44596</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44445</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>44239</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45547</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45264</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44448</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45688</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45303</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>44728</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>44089</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45711</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45075</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45561</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45775</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44089</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44068</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44152</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44575</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>44090</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45071</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44967</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>44676</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45082</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45701.45637731482</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>44102</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45097</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44895</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>44181</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>44965</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45110</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>44967</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44950</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45457</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45399</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45399</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>44169</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45439</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>45688</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45182</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45771</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44756</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44953</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>44435</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45002</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45034</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45091</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>44971</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44137</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45117</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45117</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45568</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45061</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45117</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45117</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45188</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>44316</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>44425</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45303</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45601</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>44110</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44967</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44904</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44620</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45755</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45306</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45002</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45002</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45344</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45616</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45275</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45175</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44470</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44995</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45622</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45117</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45547</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45005</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45608</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45519</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45670</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>44529</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45777</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45447</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45155</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45155</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>44147</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45261</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>44495</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45546</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45429</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45164</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45705.39993055556</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>44490</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>44467</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29553,7 +29553,7 @@
         <v>45261</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44783</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>44705</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45266</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44928</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45071</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45103</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>45679</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45230</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>44783</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45511</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>44804</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>44804</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45345</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45252</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44407</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45594</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45345</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45590</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45167</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44683</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45772</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33583,7 +33583,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>44463</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34158,7 +34158,7 @@
         <v>44102</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34329,7 +34329,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>44229</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45362</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>44939</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>44078</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45014</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44134</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35298,7 +35298,7 @@
         <v>44936</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45160</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>44900</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45139</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>44820</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45078</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36158,7 +36158,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44937</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>44426</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45328</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44582</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37137,7 +37137,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>44728</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45007</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45574.59</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45173</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45798</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45727</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45341</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45191</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39380,7 +39380,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39437,7 +39437,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45085</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>44820</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>44095</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>44111</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>44963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45097</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40188,7 +40188,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40359,7 +40359,7 @@
         <v>44984</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>44159</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45418</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45756</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>44938</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45439</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>44951</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45036</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>44624</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45299</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>44875</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45001</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45261</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44370</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>45049</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>44124</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>44911</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45170</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44313</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44945</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>44949</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45155</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45579</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>45568</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45772</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45036</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>44302</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>44145</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>44082</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45329</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>44524</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45103</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>44265</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45722</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45183</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45183</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>44391</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>45873</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>45474</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>44994</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45726.39961805556</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>44609</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>44168</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45559</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45201</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>44110</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44250</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>44454</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>44936</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45152</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45680</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>44852</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49202,7 +49202,7 @@
         <v>45574</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45467</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49373,7 +49373,7 @@
         <v>45467</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>45467</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49487,7 +49487,7 @@
         <v>45215</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49544,7 +49544,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45547</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49658,7 +49658,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>44795</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45443</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45880</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50176,7 +50176,7 @@
         <v>45182</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         <v>44984</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50518,7 +50518,7 @@
         <v>45082</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         <v>45833</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45877</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>44070</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51264,7 +51264,7 @@
         <v>44075</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45841</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51549,7 +51549,7 @@
         <v>45559</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>44867</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45188</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51777,7 +51777,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>44634</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>44071</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>44078</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45559</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>44462</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>44070</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45329</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45432</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -52999,7 +52999,7 @@
         <v>45887.57631944444</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53056,7 +53056,7 @@
         <v>45887.58039351852</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         <v>45091</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53170,7 +53170,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53341,7 +53341,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>45266</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53517,7 +53517,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>44698</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>44904</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45887.54020833333</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -53983,7 +53983,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54097,7 +54097,7 @@
         <v>44964</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54211,7 +54211,7 @@
         <v>45012</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54325,7 +54325,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>44602</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54439,7 +54439,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>45051</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>45211</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>44258</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55123,7 +55123,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45890.36122685186</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         <v>44685</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>44685</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55527,7 +55527,7 @@
         <v>45671</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>44790</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55698,7 +55698,7 @@
         <v>45755</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55755,7 +55755,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55812,7 +55812,7 @@
         <v>44091</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55869,7 +55869,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>44343</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -55983,7 +55983,7 @@
         <v>45264</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56154,7 +56154,7 @@
         <v>45093</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45138</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56325,7 +56325,7 @@
         <v>44984</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45559</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56439,7 +56439,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>44895</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56553,7 +56553,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56724,7 +56724,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>44211</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56895,7 +56895,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -56952,7 +56952,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57009,7 +57009,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>45005</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45299</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45574</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45574</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45574</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>44935</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45631</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>44134</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>45117</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>45002</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57693,7 +57693,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>45229</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57864,7 +57864,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>45895</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44126</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45208</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44791</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44992</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44872</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>44489</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45736</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44096</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45182</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>44729</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45895.5059375</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45898.45767361111</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>44984</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45341</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45322</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44209</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44160</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44334</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44245</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44152</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44732</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44875</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44813</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44186</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44201</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44272</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44326</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44186</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44452</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>44298</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>44755</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44713</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44424</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44445</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44194</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44412</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44168</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44199</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44332</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44351</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44813</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44426</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44575</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44819</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44285</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44376</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44102</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44690</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44111</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44644</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44627</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44083</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44183</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44102</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44238</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>44167</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44789</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44508</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44173</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44546</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44082</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44424</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44078</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44265</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44272</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>44259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44756</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44722</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44511</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>44407</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44460</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44839</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44879</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44298</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44447</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44532</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44798</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44648</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44376</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44182</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44608</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44417</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>44481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44106</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44474</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44494</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44187</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44179</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44791</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>44343</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44420</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44441</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44371</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44417</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44414</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44428</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44820</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44468</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44523</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44620</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44139</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44420</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44312</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44096</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44089</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44089</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44756</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44578</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45173</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44313</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44820</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>44875</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>44596</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>44490</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44239</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45170</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44250</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44102</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44875</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45341</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45329</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44967</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45362</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45097</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45091</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44448</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45432</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>44953</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45670</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45519</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44904</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45777</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44949</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45002</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45594</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45252</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45590</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45546</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45117</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45117</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45275</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>44945</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44524</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44095</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45049</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45679</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45097</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45467</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45467</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45467</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44783</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45511</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45085</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44783</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45230</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45266</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44082</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44467</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45345</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45345</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44575</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44620</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45160</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45155</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45631</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45005</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>44795</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45798</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44936</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44091</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44911</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45329</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>44895</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45559</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45559</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45362</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45152</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45727</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44134</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44582</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45191</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45078</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44995</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45175</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45082</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45671</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45561</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45001</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45418</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>45012</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45014</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>44676</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45547</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45264</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>44939</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44936</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45568</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45215</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45155</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45155</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44152</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45138</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44820</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45439</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44169</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45071</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45344</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45211</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44470</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45182</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>44963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44609</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44229</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45873</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45183</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45183</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>44685</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>44685</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35204,7 +35204,7 @@
         <v>45117</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44302</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>44728</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44728</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45182</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44454</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>44705</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>44852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44265</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45164</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>44463</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>44462</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45579</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45574</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45574</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45574.59</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45833</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>44984</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45117</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45236</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45299</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45007</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45303</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45608</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45880</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>45756</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45877</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45775</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>44804</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45299</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45266</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45306</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45841</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45061</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>44804</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>44756</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45399</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45887.57631944444</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45887.58039351852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>44867</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45547</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44950</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>45887.54020833333</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45082</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>45890.36122685186</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>44951</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45264</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45891</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45201</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45303</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45896.51149305556</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45399</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>45616</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45896.5199537037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45896.51361111111</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45895.48666666666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44483,7 +44483,7 @@
         <v>45429</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45898.30258101852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>45897.55859953703</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45897.56900462963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45898.30145833334</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45574</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45722</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45898.41762731481</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44994</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>44078</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>44495</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>44984</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45036</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>44602</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>44529</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>44425</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44110</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>44078</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45167</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45188</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>44145</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>44391</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>45688</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>44937</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44316</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45772</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45622</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>44370</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>44967</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>44967</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>44090</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>44075</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45002</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45568</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44137</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45188</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>45071</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>44110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>45002</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49633,7 +49633,7 @@
         <v>44938</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>44790</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>44698</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45082</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44134</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>44147</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45261</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>44211</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45036</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45439</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>44168</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45447</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44435</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45229</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>44900</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45474</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>44904</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45261</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45075</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52156,7 +52156,7 @@
         <v>45110</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>44159</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45547</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45261</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45103</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45005</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45103</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45559</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>44965</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>44964</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>44343</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45051</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>44102</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45680</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45139</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45117</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45117</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>44426</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>44984</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45688</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>44124</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45771</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>44971</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45601</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>44258</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45755</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56461,7 +56461,7 @@
         <v>44935</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>45034</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45574</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45002</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>45328</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56860,7 +56860,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56974,7 +56974,7 @@
         <v>45443</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>44634</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>45711</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57259,7 +57259,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>45559</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57497,7 +57497,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57616,7 +57616,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>45457</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45755</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>45895</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44126</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45208</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44791</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44992</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44872</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>44489</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45736</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44096</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45182</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>44729</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45895.5059375</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45898.45767361111</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>44984</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45341</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45322</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44209</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>44160</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44334</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44245</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44152</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44732</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44875</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44813</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44186</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44201</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44272</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44326</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>44186</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>44452</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>44298</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>44755</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44713</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44424</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>44445</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44194</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44412</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>44168</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>44199</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44332</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44351</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44813</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44426</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44575</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44819</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44285</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44179</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44376</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44102</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44690</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>44111</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44644</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44627</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44083</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44183</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44467</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44102</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44238</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>44167</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44789</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44508</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44173</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44546</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44082</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>44424</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>44078</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44265</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44272</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>44259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44756</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44722</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44511</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>44407</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44460</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44839</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44879</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44298</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44447</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44532</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44798</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44648</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44376</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44182</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44608</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44417</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>44481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44106</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44474</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44494</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44187</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44179</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44791</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>44343</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44420</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>44441</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44371</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44417</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44414</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>44428</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44820</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44468</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44523</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44620</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44139</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44420</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>44312</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44096</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44089</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44089</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>44756</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>44578</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45173</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44313</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44820</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>44875</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>44596</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
         <v>44490</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>44239</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45170</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44895</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44250</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>44102</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44875</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45341</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45329</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44967</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45362</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45097</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45091</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>44448</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45432</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>44953</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>45670</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45519</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44904</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45777</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44949</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18834,7 +18834,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45002</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45594</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>45252</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>45590</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44181</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45546</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45117</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45117</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45275</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>44945</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44524</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44095</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45049</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45679</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45097</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45467</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45467</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45467</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44783</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45511</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>45085</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44783</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45230</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45266</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44082</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>44467</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45345</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44407</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45345</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44575</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44620</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45160</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45155</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45631</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45005</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>44795</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45798</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44936</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44091</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>44911</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45329</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>44895</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45559</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45559</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45362</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45152</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45727</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44134</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44582</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45191</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45078</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>44995</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44683</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45175</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45082</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45671</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45561</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29858,7 +29858,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45001</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45418</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>45012</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45014</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>44676</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>44624</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45547</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45264</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>44939</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44936</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45568</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45215</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45155</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45155</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44152</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45138</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44820</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45439</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>44169</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45071</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45344</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45211</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>44470</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>45182</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>44963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>44609</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44229</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45873</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45183</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45183</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>44685</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>44685</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35204,7 +35204,7 @@
         <v>45117</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44302</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>44728</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44728</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45182</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35717,7 +35717,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>44454</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>44705</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>44852</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44265</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36857,7 +36857,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
         <v>45164</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37142,7 +37142,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>44463</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>44462</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45579</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45574</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45574</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45574.59</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37883,7 +37883,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37940,7 +37940,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>45833</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>44984</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>45117</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45236</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45299</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38686,7 +38686,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38857,7 +38857,7 @@
         <v>45007</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45303</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45608</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45880</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         <v>45756</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45877</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45775</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>44804</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45299</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45266</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>45306</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45841</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45061</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>44804</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>44756</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45399</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45887.57631944444</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45887.58039351852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>45093</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>44867</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45547</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44950</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>45887.54020833333</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45082</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42706,7 +42706,7 @@
         <v>45890.36122685186</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>44951</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45264</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45891</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45201</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43509,7 +43509,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43566,7 +43566,7 @@
         <v>45303</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43680,7 +43680,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43737,7 +43737,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45896.51149305556</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45399</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>45616</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45896.5199537037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45896.51361111111</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45895.48666666666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44483,7 +44483,7 @@
         <v>45429</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45898.30258101852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44830,7 +44830,7 @@
         <v>45897.55859953703</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44887,7 +44887,7 @@
         <v>45897.56900462963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45898.30145833334</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45574</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>45722</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45898.41762731481</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44994</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>44078</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>44495</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45519,7 +45519,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>44984</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45633,7 +45633,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45036</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>44602</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>44529</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>44425</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44110</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>44078</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45167</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45188</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>44145</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>44391</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>45688</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>44937</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44316</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45772</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45622</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>44370</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>44967</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>44967</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>44090</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>44075</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45002</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45568</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44137</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45188</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>45071</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49063,7 +49063,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49234,7 +49234,7 @@
         <v>44110</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>45002</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49633,7 +49633,7 @@
         <v>44938</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49690,7 +49690,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49804,7 +49804,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49861,7 +49861,7 @@
         <v>44790</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>44698</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50146,7 +50146,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45082</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>44134</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50431,7 +50431,7 @@
         <v>44147</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45261</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>44211</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50949,7 +50949,7 @@
         <v>45036</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51006,7 +51006,7 @@
         <v>45439</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>44168</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45447</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51291,7 +51291,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>44435</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45229</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>44900</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45474</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>44904</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45261</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45075</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52156,7 +52156,7 @@
         <v>45110</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52327,7 +52327,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>44159</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45547</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45261</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45103</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52902,7 +52902,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45005</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45103</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53425,7 +53425,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45559</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>44965</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>44964</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>44343</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45051</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54223,7 +54223,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54280,7 +54280,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>44102</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54508,7 +54508,7 @@
         <v>45680</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>45139</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>45117</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45117</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>44426</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55078,7 +55078,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>44984</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45688</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>44124</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45771</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>44971</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>45601</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -55995,7 +55995,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>44258</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56109,7 +56109,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45755</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56461,7 +56461,7 @@
         <v>44935</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>45034</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45574</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56689,7 +56689,7 @@
         <v>45002</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56746,7 +56746,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56803,7 +56803,7 @@
         <v>45328</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56860,7 +56860,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -56974,7 +56974,7 @@
         <v>45443</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>44634</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57088,7 +57088,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>45711</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57259,7 +57259,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>45559</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57497,7 +57497,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57559,7 +57559,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57616,7 +57616,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>45457</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45755</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57901,7 +57901,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58015,7 +58015,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>45895</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>44980</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44126</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45208</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44791</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44992</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>44872</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>44984</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45182</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45736</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45833</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45895.5059375</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45898.45767361111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>44729</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44096</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>45341</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>45322</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>44489</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>44209</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44160</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44334</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44245</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44152</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44732</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>44875</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44813</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44186</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44201</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44272</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44326</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44186</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44452</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44298</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44755</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44713</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44424</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44445</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44194</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44412</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44332</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44168</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44199</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44351</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44813</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44426</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44575</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44285</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>44819</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>44179</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44376</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44102</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>44690</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44865</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>44111</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44644</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>44627</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44083</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44183</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>44438</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44102</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44238</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44238</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44167</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44789</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44508</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44173</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>44546</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44082</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44424</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44265</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44272</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>44259</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44722</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44756</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44511</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44407</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>44460</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44839</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44879</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44298</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44447</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44532</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44489</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>44376</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>44648</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>44798</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44182</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44608</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44417</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44106</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44474</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44494</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44179</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44187</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44791</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44343</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44420</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44371</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44441</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>44417</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44820</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44468</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44414</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44428</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44116</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44523</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44139</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44420</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44620</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44312</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44756</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44578</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44445</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44596</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45457</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45399</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45399</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44089</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>44089</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>44239</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44875</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44448</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44435</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45688</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44728</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45075</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45561</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45034</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45091</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45616</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45275</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45175</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45775</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45002</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45002</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45519</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45670</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45777</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44971</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45117</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45117</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>44470</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45188</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>44995</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45622</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45546</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45117</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45547</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45303</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44967</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>44676</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44783</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45266</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45362</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>44967</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>45082</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45005</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45679</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45230</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>44783</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45511</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45345</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44895</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45252</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>44407</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45594</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45345</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>44904</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45306</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45590</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45261</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45344</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44495</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44181</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44965</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45429</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45110</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45539.6015162037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45261</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44705</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45608</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44529</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45447</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45155</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45155</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44147</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45164</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44490</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44467</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44928</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45071</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45103</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44463</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>44102</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>44804</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>44804</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>44229</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44939</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45167</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44683</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45798</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44936</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45160</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28887,7 +28887,7 @@
         <v>45139</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44820</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45727</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45078</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45328</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>44728</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45007</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45362</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45014</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45394.42223379629</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>44134</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>44900</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45341</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>44820</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>44937</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44901.44304398148</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44426</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>44159</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>44582</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45418</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45756</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45439</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45574.59</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45173</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>44624</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45299</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33928,7 +33928,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34042,7 +34042,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>45191</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>44875</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35430,7 +35430,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35487,7 +35487,7 @@
         <v>45873</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>45261</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>44609</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45085</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36357,7 +36357,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>45880</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45877</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>44095</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45841</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45097</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44124</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>45887.57631944444</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>45887.58039351852</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44911</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44313</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45887.54020833333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38419,7 +38419,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>44984</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45890.36122685186</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>45895.48666666666</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45891</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>45896.5199537037</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         <v>45897.55859953703</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>44938</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45897.56900462963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>45896.51149305556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>45896.51361111111</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>45898.41762731481</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45898.30145833334</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>45898.30258101852</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45579</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45568</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>45772</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>45903.55202546297</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45902.7003125</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>45902.70890046296</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45903.51274305556</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>44951</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>45036</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>44302</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>44082</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45904.31614583333</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45329</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45905.66465277778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41242,7 +41242,7 @@
         <v>44524</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45001</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45903.55363425926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>44370</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41822,7 +41822,7 @@
         <v>45904.42247685185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>44265</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45236</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42226,7 +42226,7 @@
         <v>45049</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45170</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42459,7 +42459,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42516,7 +42516,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>44945</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>44949</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>44994</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>44168</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43086,7 +43086,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>45201</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45036</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43428,7 +43428,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44250</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>44145</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45308.50334490741</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>45152</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>45680</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>45574</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45103</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>45215</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45547</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>45722</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45183</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>45183</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>44391</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44795</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45474</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>45559</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45443</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44110</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45182</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45644.55559027778</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44984</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46003,7 +46003,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46060,7 +46060,7 @@
         <v>44454</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44936</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45559</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>44867</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46516,7 +46516,7 @@
         <v>45188</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>44852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45467</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45467</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45467</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45559</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45329</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45432</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45082</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45091</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>44698</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48028,7 +48028,7 @@
         <v>45713.42976851852</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>44634</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>44602</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44462</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45051</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45266</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48945,7 +48945,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>44685</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>44685</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>44904</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45671</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>45755</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>44964</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45012</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>44343</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45138</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>44984</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45211</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45559</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>44258</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>44211</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50831,7 +50831,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44790</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45005</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45299</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>45117</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51230,7 +51230,7 @@
         <v>44091</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45303</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45711</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45264</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45093</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>44152</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>44895</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51976,7 +51976,7 @@
         <v>44575</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52033,7 +52033,7 @@
         <v>44090</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45071</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52375,7 +52375,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45574</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>45574</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         <v>45574</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         <v>44935</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>45631</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52774,7 +52774,7 @@
         <v>44134</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52888,7 +52888,7 @@
         <v>45002</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45071</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45229</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53230,7 +53230,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>44967</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45547</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>45264</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>44169</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45082</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54266,7 +54266,7 @@
         <v>45182</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54323,7 +54323,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54380,7 +54380,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54437,7 +54437,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54613,7 +54613,7 @@
         <v>44102</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54727,7 +54727,7 @@
         <v>45097</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54784,7 +54784,7 @@
         <v>45726.44111111111</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54903,7 +54903,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>44950</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55017,7 +55017,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55131,7 +55131,7 @@
         <v>45439</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45688</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55302,7 +55302,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55416,7 +55416,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45601</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55644,7 +55644,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55701,7 +55701,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45771</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>44756</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55929,7 +55929,7 @@
         <v>44953</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>44110</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45002</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56390,7 +56390,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>44620</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56514,7 +56514,7 @@
         <v>44137</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56571,7 +56571,7 @@
         <v>45755</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56742,7 +56742,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56913,7 +56913,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57027,7 +57027,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57084,7 +57084,7 @@
         <v>45568</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57141,7 +57141,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57255,7 +57255,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>45061</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45117</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>45117</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57545,7 +57545,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>44316</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57773,7 +57773,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>44425</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57887,7 +57887,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57944,7 +57944,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58001,7 +58001,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -58115,7 +58115,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -58172,7 +58172,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -58229,7 +58229,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>45895</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44126</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45208</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44791</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44992</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44872</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>44489</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45736</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44096</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45182</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>44729</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45833</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45895.5059375</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>45898.45767361111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44984</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45322</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>44209</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44160</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44334</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44245</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44152</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>44875</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44732</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44813</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>44201</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44272</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44326</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44186</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44452</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44186</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>44460.54369212963</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44298</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44539.38949074074</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44755</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>44713</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44356.4577662037</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44424</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44445</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44412</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44194</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44332</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44168</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>44199</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>44452.57429398148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>44351</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44489.36836805556</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>44813</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44524.60759259259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44426</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44865.31504629629</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44753.64795138889</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>44533.37256944444</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44575</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44819</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>44285</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>44179</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44230.58090277778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44376</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44461.58863425926</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>44570.7678125</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44102</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44494.43064814815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44641.41877314815</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>44692.6459375</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>44690</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>44470.63061342593</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44610.61052083333</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44865</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>44111</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44791.5112962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44644</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44603.34966435185</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>44627</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44183</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44804.43328703703</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44180</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>44102</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44467</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44452.57803240741</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44238</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44238</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44292</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44167</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44789</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44508</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44173</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>44546</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>44388.75799768518</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44424</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>44265</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44298.48719907407</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44272</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44327.36415509259</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>44722</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44722.47052083333</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>44756</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44867.48452546296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44259</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>44511</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>44407</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>44460</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44330.85600694444</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>44839</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>44879</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44298</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44347.37032407407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44364.57402777778</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44791.50940972222</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44447</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>44875.48474537037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44532</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44455</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>44459.41479166667</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44879.36677083333</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44267.52525462963</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44595.53346064815</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>44494.42767361111</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44466.60142361111</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44369.60105324074</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44456.47127314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44489</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44529.64541666667</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44631.51841435185</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44376</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>44798</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44648</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>44182</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>44427.38479166666</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44266.64517361111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44608</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44417</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44448.62255787037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44448.62701388889</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44481</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44620.48642361111</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44620.56289351852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44452.59166666667</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44636.91965277777</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44106</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44474</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44302.41256944444</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44494</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44519.39663194444</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44243.44302083334</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44698.44061342593</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44685.90943287037</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44187</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44791</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44711.4805324074</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44748.33731481482</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44641.41453703704</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44509.57108796296</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44522.40835648148</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44533.36805555555</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>44722.49434027778</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>44441</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>44417</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44539.36767361111</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44343</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>44139.56196759259</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44685</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44371</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>44116</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44753.66400462963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>44540.34863425926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>44631.46165509259</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44888.46783564815</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>44420</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44820</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44676.45506944445</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>44334.62680555556</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44468</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44698</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44680.58664351852</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44180.53715277778</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44139.6122337963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44139</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44224.64115740741</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44306.65480324074</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44753.5284375</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44523.41112268518</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44420</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44631.64724537037</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44523</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44375.38892361111</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44312</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44096</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44712.58903935185</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44578</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44463.34797453704</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44756</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44371.61570601852</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44749.62980324074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44089</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44596</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44089</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45362</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45173</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44313</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44239</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44414</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44285.60979166667</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44769.55420138889</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44820</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>45720.30268518518</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>44428</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44490</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45338.61513888889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45411.88930555555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45412.33927083333</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44102</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44875</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>45720.54211805556</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44250</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45395.6982175926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45702.43898148148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44448.61657407408</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45341</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45097</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45091</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45329</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45553.89721064815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45170</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45432</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44895</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45330.61230324074</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45194.5039699074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44960.35675925926</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44967</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44950.55744212963</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45252.60836805555</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>45327.82945601852</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45432.37760416666</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45681.57925925926</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45370.43637731481</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44448</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>45240.39980324074</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45434.50174768519</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44376.60693287037</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45408.34063657407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44481.71842592592</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45349.62076388889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45758.41039351852</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44953</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45274.60413194444</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45300.4487962963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45670</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45562.33819444444</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45419.61716435185</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45519</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45574.59706018519</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45089.63065972222</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>45602.49121527778</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>44904</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45777.34246527778</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45325.3631712963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45615.52241898148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45777</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45107.63880787037</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45777.54184027778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45777.54693287037</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45278.46920138889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>44446.48659722223</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45777.71884259259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45449.62283564815</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>45449.62583333333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44883.55409722222</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45240.38824074074</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45782.62265046296</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44949</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44949.44320601852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45002</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45782.61675925926</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45314.69070601852</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45394.34818287037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45784.48793981481</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45392.35590277778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45769.40989583333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45553.43114583333</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>44109.47537037037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45784.4921412037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45069.57748842592</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45275</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44838.42135416667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44545.69108796296</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44945</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44524</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>44095</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44881.59844907407</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45424.34530092592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45019.64087962963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45594</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>44181</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44930.58833333333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45252</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45590</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45089.63690972222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45117</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45117</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45049</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45097</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45785.32844907408</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45439.46385416666</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45786.46171296296</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45546.66178240741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45546</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45679.65525462963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45467</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45467</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45709.60627314815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45467</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45176.58252314815</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45455.58665509259</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>44111</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45785.54833333333</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45670.48797453703</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>44928.57497685185</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45679</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44783</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45726.34025462963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45252.57751157408</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>44964.34165509259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45477.3696412037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45568.36784722222</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45562.70030092593</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45511</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45533.54414351852</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>44903.32229166666</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45636.36040509259</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45597.63311342592</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45524.58696759259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22069,7 +22069,7 @@
         <v>45576.55013888889</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45565.32006944445</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45085</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45445.42417824074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45250.43831018519</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45166.33278935185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44783</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45230</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44620</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>45546.58138888889</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45266</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44467</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45789.38111111111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45789.38739583334</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>44558.59878472222</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45789.39083333333</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45712.55288194444</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45345</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>44540.33586805555</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45789.36847222222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45461.85684027777</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45637.31363425926</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45345</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45342.61726851852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44489.36054398148</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44575</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45154.61569444444</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45436.38177083333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45152.32761574074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44620</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45274.61003472222</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>44545.69075231482</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>44445</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45155.57315972223</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45155</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45635.47542824074</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44540.35796296296</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>45540.64592592593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>45758.41546296296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45631</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45635.47096064815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45310.42872685185</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45600.45130787037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45792.53266203704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45793.60109953704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45475.38958333333</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45793.61269675926</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45793.59478009259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45548.37193287037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>44795</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45793.67645833334</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>45796.39645833334</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45436.36854166666</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45793.67784722222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>45005</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45033.46269675926</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>44570.82280092593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>44550.91732638889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45793.59197916667</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45107.6415162037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44586.42520833333</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45798</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>44936.62181712963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44936</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45631.62325231481</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45559</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45559</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45246.34444444445</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45798.66282407408</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45152</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>45671.45043981481</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45742.31431712963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
         <v>45800.56369212963</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45800.57278935185</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>45644.59047453704</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45644.43983796296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>44582</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45394.33961805556</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45191</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44091</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44911</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45329</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45078</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44895</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         <v>45692.37760416666</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45727.33197916667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45800.43210648148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44875</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44683</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45478.71304398148</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45533.27699074074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>45477.37409722222</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45540.55045138889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>44481.71746527778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45618.40965277778</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45408.29181712963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45175</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45637.3166087963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45426.43824074074</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45739.78570601852</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45203.38741898148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45362</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28047,7 +28047,7 @@
         <v>45646.8040625</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45684.52679398148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45803.84655092593</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>45727</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45082</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>45180.46916666667</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>45372.51082175926</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45191.32893518519</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45664.49270833333</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45106.82878472222</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44134</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45728.68841435185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>44907.72450231481</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28793,7 +28793,7 @@
         <v>45539.60410879629</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>44599.69871527778</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45805.65516203704</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45085.68162037037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>45107.41297453704</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44930.58310185185</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>44627.6955787037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>44995</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>44624</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45547</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45176.46469907407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45155.72224537037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45215.42108796296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>45609.47512731481</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44621.48859953704</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>44614.42685185185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>45671</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45561</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45210.36392361111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         <v>44288.50678240741</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>45553.64894675926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44928</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30052,7 +30052,7 @@
         <v>45215</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45001</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45147.59756944444</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45418</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         <v>45811.49784722222</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30342,7 +30342,7 @@
         <v>45007.97726851852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44971.51954861111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44152</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45138</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45713.43387731481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>45090.69125</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>44820</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45012</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45014</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>44676</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>44950.55974537037</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45635.47998842593</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>44965.48167824074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>44945.43136574074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31150,7 +31150,7 @@
         <v>45264</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45264.80452546296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>44939</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45029.70599537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31378,7 +31378,7 @@
         <v>45244.5584375</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45574.6072337963</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45695.38024305556</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45700.4653587963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45245.43540509259</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45211</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44657.34813657407</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45240.3635300926</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45684.55307870371</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45553.66137731481</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44936.61140046296</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44936</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45700.4577199074</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45568</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45820.36880787037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45183</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45183</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45117</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>44302</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>44749.61423611111</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45793.58851851852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45803.88311342592</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>44617.58907407407</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>44728</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44728</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45173.37136574074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45728.68726851852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45155</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45155</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44655.47528935185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45226.57850694445</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45821.34012731481</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44700.65032407407</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>44620.55774305556</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33331,7 +33331,7 @@
         <v>45181.53826388889</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45820.78407407407</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44705</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>45825.70871527777</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45614.33466435185</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>44852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45439.46791666667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44265</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44753.66082175926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45308.48898148148</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45164</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45164.6913425926</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45825.41503472222</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44169</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45197.63037037037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45637.31768518518</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>44928.39131944445</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45827.38292824074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45071</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45874.68646990741</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45831.74694444444</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45344</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45873.62280092593</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45264.80158564815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45548.36065972222</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45117</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>44609</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45236</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45299</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45331.49637731481</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45831.75487268518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45832.55674768519</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45303</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45873</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45873.61965277778</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>44470</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44928.37655092592</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45832.49506944444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45873.45962962963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45873.48318287037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45182</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45238.45707175926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45702.48780092593</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45162.46358796296</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45109.84163194444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>45109.88641203703</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45302.6375462963</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45756</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44229</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45091</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45726.41037037037</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45833.55179398148</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45267.54662037037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45833.55715277778</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45775</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>44685</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>44685</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45875.59371527778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45833.60056712963</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45834.49486111111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>44993.38681712963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>44804</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45182</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45299</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>45695.38659722222</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>45077.50006944445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>44266.43513888889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>44454</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>44673.64371527778</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>45876.65726851852</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45462.34165509259</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>45614.3747337963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37512,7 +37512,7 @@
         <v>45107.30564814815</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>44620.35722222222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>44230.64799768518</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45266</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45763.56696759259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45306</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
         <v>45034.46636574074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>44463</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45671.44703703704</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44462</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>45314.68846064815</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45727.45702546297</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44804</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45838.44895833333</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45434.6920949074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45579</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45574</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>45574</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45574.59</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45580.68637731481</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45580.6872337963</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45176.46609953704</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>44984</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45323.60738425926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45307.39928240741</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45007</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44312.30976851852</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45608</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45366.35745370371</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>44756</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>44901.43681712963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39284,7 +39284,7 @@
         <v>44901.44385416667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45267.48949074074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45882.43188657407</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>45399</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45461.56465277778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45840.47287037037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45061</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44904.48119212963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44867</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44390.6009837963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>44950</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45706.58024305556</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45881.47059027778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>45881.47516203704</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>44545.69655092592</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>44831.61528935185</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40201,7 +40201,7 @@
         <v>44831.61790509259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45839.59809027778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45119.4822337963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>44522.34871527777</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>45082</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45880</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45062.41892361111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45009.68813657408</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44993.65773148148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>45096.65381944444</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45610.40166666666</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45002.41061342593</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45674.4733449074</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45881.4999537037</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>45093</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44998.39121527778</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45547</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45839.59554398148</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44951</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>45552.66143518518</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>45327.82774305555</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45629.67857638889</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>45629.68018518519</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>44748.32376157407</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45272.58155092593</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45264</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45701.45875</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45877</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41812,7 +41812,7 @@
         <v>45099.52606481482</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45469.46677083334</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>45727.4515625</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45617.87607638889</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>45201</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>44748.32592592593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>45121.37194444444</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44691.57900462963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45646.7996412037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45303</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>45728.68474537037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45884.46671296296</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45722</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45399</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45616</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44994</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>45728.68342592593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>44495</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>44505.56627314815</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45841.90819444445</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45841</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>45062.41542824074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45078.66384259259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>44977.41337962963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45036</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45644.39822916667</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45646.79543981481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45035.56302083333</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>44529</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45429</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45429.37171296297</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45201.86790509259</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>44930.60707175926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45678.43621527778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45167</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45188</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45710.3284375</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>44391</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45688</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44937</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>45188.57582175926</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45772</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45622</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45247.56596064815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44991.37030092593</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>44991.37282407407</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45247.56952546296</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45247.57582175926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>44988.39340277778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45113.43203703704</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45110.37491898148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44729,7 +44729,7 @@
         <v>45685.49436342593</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>45244.59684027778</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>45063.50965277778</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45063.51554398148</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44446.56373842592</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45014,7 +45014,7 @@
         <v>45574</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45002</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>44930.59520833333</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45197.63912037037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45841.91457175926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45386.59690972222</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>44627.42074074074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45264.80734953703</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45071</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45071</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45071.61512731481</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45260.57837962963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>44631.46039351852</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45112.54576388889</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45735.76244212963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45735.76439814815</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45466.61302083333</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>44473.47971064815</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>44790</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45412.33401620371</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45082</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45082.41980324074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44134</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>44147</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45106.86053240741</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>44916.42804398148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45261</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45709.56060185185</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>44984</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45371.52966435185</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>44211</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45406.56274305555</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45884.4652662037</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45439</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>44168</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45635.46958333333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45757.32127314815</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47133,7 +47133,7 @@
         <v>45677.59115740741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>44435</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>44427.54488425926</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45229</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>44602</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45407.56440972222</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45075</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45110</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45107.45663194444</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>44425</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>44110</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45887.57631944444</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45887.58039351852</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45726.40527777778</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45261</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45887.54020833333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45103</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>44657.40945601852</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45183.60244212963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>44145</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48288,7 +48288,7 @@
         <v>45755.74106481481</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>44316</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45848.61209490741</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45848.61425925926</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45751.74186342592</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48578,7 +48578,7 @@
         <v>45890.36122685186</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>44483.60684027777</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>44370</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>44967</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>45103</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>45572.43400462963</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>44628.67694444444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
         <v>45559</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45109.83387731481</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>44967</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45034.29767361111</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>44090</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>44939.42466435185</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>44988.38652777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45568</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45891</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44137</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>44452.5708912037</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45751.41162037037</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45896.51149305556</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45188</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45896.5199537037</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45062.5940162037</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45395.69365740741</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45896.51361111111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45895.48666666666</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45002</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45898.30258101852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45897.55859953703</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45897.56900462963</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45898.30145833334</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45600.51381944444</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45898.41762731481</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>44938</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>44909.56182870371</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>44698</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45331.35601851852</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45331.35946759259</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45331.3629050926</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45155.56731481481</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>44509.57325231482</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>44740.4180324074</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45176.46045138889</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45359.52144675926</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45036</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45384.37467592592</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45447</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44818.77861111111</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51329,7 +51329,7 @@
         <v>44930.61665509259</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45902.7003125</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44428.62381944444</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51500,7 +51500,7 @@
         <v>44631.53199074074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
         <v>45904.42247685185</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>44900</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>45903.55202546297</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45902.70890046296</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>45903.51274305556</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>45903.55363425926</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>45553.65998842593</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -51971,7 +51971,7 @@
         <v>45904.31614583333</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52033,7 +52033,7 @@
         <v>45474</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45685.41125</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>44904</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45261</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45908.61346064815</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52318,7 +52318,7 @@
         <v>45908.6147337963</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52375,7 +52375,7 @@
         <v>44967.4374537037</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>44967.48209490741</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>44518.26645833333</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>44159</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45607.56002314815</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45547</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45684.55832175926</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52779,7 +52779,7 @@
         <v>45908.47</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -52836,7 +52836,7 @@
         <v>45086.72387731481</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45905.66465277778</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45674.4681712963</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>45090.69401620371</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45005.39861111111</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45005</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53178,7 +53178,7 @@
         <v>44179</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45252.56825231481</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53292,7 +53292,7 @@
         <v>45701.45229166667</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45547.43822916667</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>45644.55795138889</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>45698.40377314815</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45909.74082175926</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>45911.5083912037</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>45106.30399305555</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>44965</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>44964</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>44712.45701388889</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>44299.58810185185</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>44343</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45051</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>44599.46640046296</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>45033.56914351852</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54147,7 +54147,7 @@
         <v>45911.51158564815</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>45129.5234375</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54261,7 +54261,7 @@
         <v>44895.51835648148</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>44916.42905092592</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54375,7 +54375,7 @@
         <v>44972.4353587963</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>45601.67561342593</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>44102</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54546,7 +54546,7 @@
         <v>45680</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>45139</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45117</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>45117</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>45082.45512731482</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>45646.61111111111</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>44888.47229166667</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45377.44168981481</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55002,7 +55002,7 @@
         <v>44426</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55059,7 +55059,7 @@
         <v>45215.35358796296</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>45394.32820601852</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55173,7 +55173,7 @@
         <v>45035.58140046296</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45401.35483796296</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>44984</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55344,7 +55344,7 @@
         <v>45688</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>45755.56081018518</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>44124</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>45279.36726851852</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -55572,7 +55572,7 @@
         <v>45331.36413194444</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45771</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>45240.37677083333</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -55743,7 +55743,7 @@
         <v>44949.4493287037</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -55800,7 +55800,7 @@
         <v>44971</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -55857,7 +55857,7 @@
         <v>45601</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45758.41136574074</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45574.71269675926</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>44258</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45356.56041666667</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -56152,7 +56152,7 @@
         <v>45758.4091550926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>45755</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -56271,7 +56271,7 @@
         <v>45755.48774305556</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>45727.42905092592</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>45579.4727662037</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>44935</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45034</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -56556,7 +56556,7 @@
         <v>45763.27762731481</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>45574</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>45002</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -56727,7 +56727,7 @@
         <v>45124.51753472222</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>45328</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -56841,7 +56841,7 @@
         <v>44960.56908564815</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -56898,7 +56898,7 @@
         <v>45553.6357175926</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -56955,7 +56955,7 @@
         <v>45443</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>44634</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -57069,7 +57069,7 @@
         <v>45702.49078703704</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>45394.33746527778</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -57183,7 +57183,7 @@
         <v>45711</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45439.42700231481</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -57297,7 +57297,7 @@
         <v>45691.71813657408</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -57359,7 +57359,7 @@
         <v>45559</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>45637.3090162037</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45637.31978009259</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -57540,7 +57540,7 @@
         <v>45615.52596064815</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -57597,7 +57597,7 @@
         <v>45540.59579861111</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45457</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>45267.54905092593</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45755</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45474.37907407407</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>45386.66395833333</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45596.8827662037</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -567,7 +567,7 @@
         <v>44980</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>45895</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44126</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45208</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44791</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>45789.4197337963</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>44992</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45810.5565162037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>45751.72659722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>44872</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>45099.51319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44599.69256944444</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>44489</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45387</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45546.56554398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45736</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>44992.68729166667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>44096</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45182</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45827.50682870371</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>44729</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>45833</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45842.29693287037</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>45565.49403935186</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45406.55770833333</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45849.56431712963</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45895.5059375</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>45898.45767361111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44984</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45341</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>45322</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>44209</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44160</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>44888.43023148148</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>44285.63270833333</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44334</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44245</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44557.47803240741</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44152</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44841.49872685185</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>44875</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44732</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>44620.55424768518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44620.56054398148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>44453.56091435185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>44813</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44508.83615740741</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>44875.47472222222</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44218</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44356.46040509259</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>44201</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44272</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>44174</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44326</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44186</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44452</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44186</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</